--- a/sources/armorking_step7.xlsx
+++ b/sources/armorking_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA105"/>
+  <dimension ref="A1:AB105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="133" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>f9ce71ca-5aa2-4481-be55-3310546052c7</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0f9bdab1-75b2-4228-a53f-f0a45e37e195</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>5fc6512a-4404-42e6-80c3-2fc278d4455b</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>06dc090e-c5ae-46e1-a19f-d04e3a8a5207</t>
         </is>
@@ -783,12 +789,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>898e20e1-c3e0-43e8-8566-cecbdaf86347</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>8c7def3b-7c4e-4924-8394-4e591d86c38d</t>
         </is>
@@ -855,12 +861,12 @@
           <t>After the initial grab, escape with 3+4.</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2ab01235-e3c3-4afb-af8d-794284dc99c9</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>aacf4303-5f8c-448b-8b48-aca54f9326dd</t>
         </is>
@@ -927,12 +933,12 @@
           <t>Can be Tech Rolled to reduce damage by half.</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>58992924-7087-47b9-a190-320799679b61</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>6caca9f4-1eb2-4e32-8bc0-fa8bf330f264</t>
         </is>
@@ -994,12 +1000,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>b6c967e2-9ac1-4908-863a-fcb1b0ecf168</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>f5bd83e9-96be-449f-825e-dc066deabe14</t>
         </is>
@@ -1061,12 +1067,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>a1c92638-4a1a-412d-b86d-9d6ba82425dc</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>4cd6c89f-9faf-40a3-b3b9-43495afc8252</t>
         </is>
@@ -1075,27 +1081,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D,db+2+4 [~5]</t>
+          <t>D,db+2+4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D,db+2+4 [~5]</t>
+          <t>D,db+2+4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DB+2+4 [~5]</t>
+          <t>DB+2+4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Armor King's Drver [Tag]</t>
+          <t>Armor King's Drver</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Armor King's Drver [Tag]</t>
+          <t>Armor King's Drver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1140,10 +1146,15 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>f593dcd2-96d4-4be9-9a67-c91c86c3b679</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>222011b9-5903-46a3-8fa1-df6f46daa34a</t>
         </is>
@@ -1152,22 +1163,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Frankensteiner [Tag]</t>
+          <t>Frankensteiner</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Frankensteiner [Tag]</t>
+          <t>Frankensteiner</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1212,10 +1223,15 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>120ce26e-0aee-46de-bdb2-d6d6b18c626e</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>837014c6-6dee-4ee6-98ca-785113dbadf2</t>
         </is>
@@ -1287,12 +1303,12 @@
           <t>Can be done on a face down or face up opponent.</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>0d4f502a-09d2-47d8-82ae-55e64c6b84dc</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
@@ -1349,12 +1365,12 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1401,17 +1417,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1458,17 +1474,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1520,17 +1536,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1582,17 +1598,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1649,12 +1665,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1711,12 +1727,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1773,12 +1789,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1910,20 +1926,25 @@
       </c>
       <c r="X23" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y23" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr">
+      <c r="Z23" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z23" s="1" t="inlineStr">
+      <c r="AA23" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA23" s="1" t="inlineStr">
+      <c r="AB23" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2005,12 +2026,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>425ecead-c5f5-4fae-b77d-422ca2afe090</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>a9e68546-0185-46ef-8ed4-8a0b9b10aa49</t>
         </is>
@@ -2092,12 +2113,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>3fe6d4bf-a051-4506-a70d-2bf2a0526aaa</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>454bb85d-4210-448b-80aa-39b229c5b159</t>
         </is>
@@ -2179,12 +2200,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>7b3c7523-179a-4243-b4ff-d95c3cf7da7f</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>f3bb5aa5-066e-488e-bb8c-b05561279e2e</t>
         </is>
@@ -2266,12 +2287,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>c44668fe-5287-4604-88c1-28460e83c16f</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>098a9278-c701-4eaf-a813-84fababab275</t>
         </is>
@@ -2353,12 +2374,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>b099ff65-2292-4306-9641-5df82371cb4d</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>2e7f3c76-a21f-422c-bce4-6f6b03b4d2eb</t>
         </is>
@@ -2440,12 +2461,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>46306ede-df09-4fd4-a22e-683590bcc90f</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>f5f5e160-785c-4d03-9348-c3e64c3ec8d8</t>
         </is>
@@ -2527,12 +2548,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>a5af8aee-cfb9-4150-9900-97663eaa005d</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>84e6cfd8-06a4-4792-b69b-7138dd47e6c5</t>
         </is>
@@ -2614,12 +2635,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>e86479f4-aaff-4cbe-a1d3-048dbb9eaf30</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>5070b82d-e58b-4c7b-a0f9-0db46531428d</t>
         </is>
@@ -2701,12 +2722,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>35d7bc20-c87c-4517-bc1c-0718d5232806</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>3265579b-e039-45b2-b901-9e081e404889</t>
         </is>
@@ -2788,12 +2809,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>380565ba-6f89-41ce-a448-c96ec4e77671</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>b030046c-efd4-4e98-bf03-7bd02c053fb1</t>
         </is>
@@ -2875,12 +2896,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>d9b549e9-607b-44a3-b65e-a96ad7a21365</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>c2aa915b-99b3-4dec-8030-b347566d7683</t>
         </is>
@@ -2962,12 +2983,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>eb3d8898-b370-4c3e-b890-36b9d527e7e0</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>ff3d8574-2231-47c3-9a23-da6397dfb5e2</t>
         </is>
@@ -3049,12 +3070,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>c1100dcd-7386-4729-976f-94d0c10e01b7</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>110de783-241f-4434-9ee9-b2f2282b625e</t>
         </is>
@@ -3136,12 +3157,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>68169812-6f33-4587-af9b-01f1197d41fe</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>db4c65d5-8db1-4306-8971-3e405e45dcaa</t>
         </is>
@@ -3223,12 +3244,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>80fb6cea-14ab-4952-b3c4-cc15052db610</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>9ab80fdd-fb6e-4c05-8778-dc2ff8a34308</t>
         </is>
@@ -3310,12 +3331,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>b0c18e86-cf15-46cb-9294-c345ce136d3a</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>79956f02-d230-4a3d-a91e-2278f1bc39ce</t>
         </is>
@@ -3397,12 +3418,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>2390f9cd-e831-4fcf-9a97-c7ac631288eb</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>5f415e40-13fc-4adb-bfc4-cbe236d5cb6e</t>
         </is>
@@ -3484,12 +3505,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>2bc4d065-9808-467d-b2ef-0dc9c98d6bc3</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>8442cf78-2ba8-4d81-9954-ff712f6c6bbb</t>
         </is>
@@ -3571,12 +3592,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>0048037f-4c9a-4ac7-ab8d-8d77f35ec379</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>07e44464-e8a6-43d0-b162-9ebf83073f23</t>
         </is>
@@ -3658,12 +3679,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>4ed88471-48fb-4424-b1d6-4ff05a9eafaf</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>e3b89a0c-60bc-481a-bbab-fc07eb530c67</t>
         </is>
@@ -3745,12 +3766,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>dc7b170d-9a9b-4eae-aa45-d04a9b9644b6</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>8ef29abb-51a1-4f64-b660-25cbee7be486</t>
         </is>
@@ -3832,12 +3853,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>a3f049e9-03a1-4863-aff8-6c62b22bd98e</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>bba8a28b-8fcf-4ab3-821e-44e475d24c1b</t>
         </is>
@@ -3919,12 +3940,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>9c8a2371-7cb5-4c03-9d9c-3e7be29224ca</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>14230b82-617c-4a26-9e9f-0c73ee47a678</t>
         </is>
@@ -4006,12 +4027,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>60bba712-65b9-4363-aa67-702066fa212f</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>a62d95a8-d7d1-4730-9a9f-869030cdab23</t>
         </is>
@@ -4143,20 +4164,25 @@
       </c>
       <c r="X50" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y50" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y50" s="1" t="inlineStr">
+      <c r="Z50" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z50" s="1" t="inlineStr">
+      <c r="AA50" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA50" s="1" t="inlineStr">
+      <c r="AB50" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -4253,12 +4279,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>9f288870-b237-4a2d-9722-8b59e043436a</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>354dab8e-e02a-44ab-82d3-b5d712e003f3</t>
         </is>
@@ -4355,12 +4381,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>a27064f0-da8a-4052-9014-478c07cbcb87</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>03cecdef-ae4e-408f-854b-172d760e9a7e</t>
         </is>
@@ -4457,12 +4483,12 @@
           <t>CS OBc</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>26f5fa66-8a0a-447d-b39a-41b0316ce295</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>bfecad09-d073-4d08-9852-f9229a38f6a9</t>
         </is>
@@ -4559,12 +4585,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>74775d6a-29fb-4bd6-ad28-d2be38f2e7bb</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>8e181d74-9595-4d22-83f1-5b83615ace7f</t>
         </is>
@@ -4656,12 +4682,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>9633cdef-e24e-4676-9299-3d28d609372a</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>617d3195-98c8-4793-95df-e76d67a1d361</t>
         </is>
@@ -4753,12 +4779,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>bf774eab-e828-4478-b478-d08b88a510b1</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>689069d7-667f-4b36-9163-718de6d1238d</t>
         </is>
@@ -4855,12 +4881,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>fd968785-ece3-47a5-92fc-a0d72a0c858b</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>11ed2db5-bd38-4efe-a4ca-8880fd7755c7</t>
         </is>
@@ -4952,12 +4978,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>6fec99ce-a280-4022-936b-d6a726d2c00e</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>e6281cae-4def-47e4-9be4-e118aa916f62</t>
         </is>
@@ -5054,12 +5080,12 @@
           <t>GB SLDc</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>00e3804b-a60e-4c84-a177-cd15e4735427</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>092be268-ab49-4fc0-887b-5709b7e8e802</t>
         </is>
@@ -5161,12 +5187,12 @@
           <t>Hits high at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>dca3e8a7-3253-4beb-859f-f86a91cec02e</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>39d604fa-caf6-4a30-a9ca-73c996e26573</t>
         </is>
@@ -5268,12 +5294,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>4336aca8-72e9-4de4-b567-00182e4e297d</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>0704d26e-9310-4446-b785-4426d468365b</t>
         </is>
@@ -5330,12 +5356,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>cd1e647b-0556-484d-b641-a13ba2b71ae2</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>74f706f4-4a47-403c-a8df-f18096ac7a1b</t>
         </is>
@@ -5432,12 +5458,12 @@
           <t>FSc</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>ee74f26d-769f-4df4-bbf7-7fbfb610cb9d</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>f057c9e7-f1c1-4078-995e-999034d6faf2</t>
         </is>
@@ -5539,12 +5565,12 @@
           <t>Leaves Armor King in Back Turned Position when the opponent blocks.</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>20573691-9a78-457b-8baa-ffefe9b25044</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>ca61d1a0-8d2e-46a4-98d2-0c035f774084</t>
         </is>
@@ -5553,22 +5579,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Smash Upper [Tag]</t>
+          <t>Smash Upper</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Smash Upper [Tag]</t>
+          <t>Smash Upper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5643,10 +5669,15 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>d11f5d19-7db2-4b0d-9b48-f6223d76772c</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>399faacb-83da-489a-a3c7-9b838d5a639e</t>
         </is>
@@ -5738,12 +5769,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>ebc76774-237e-42af-a946-361b5f39d9d8</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>3dbdcaa6-2488-4c15-8b53-dc33d7481626</t>
         </is>
@@ -5840,12 +5871,12 @@
           <t>DSc</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>f8b49771-5fca-4a5b-b0a8-10bed196b340</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>287a4d40-0c80-4ea4-991c-66aaefa1e92e</t>
         </is>
@@ -5854,22 +5885,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FC+df+2 [~5]</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FC+df+2 [~5]</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dynamite Upper [Tag]</t>
+          <t>Dynamite Upper</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dynamite Upper [Tag]</t>
+          <t>Dynamite Upper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5944,10 +5975,15 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>69af551b-4c75-4614-a04f-ce032a2aff16</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>765ac45b-a790-43b3-84fb-8b5da4cfe515</t>
         </is>
@@ -6044,12 +6080,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>390963d5-ab9b-4abe-b87d-b8b588084767</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>c55fd6d7-722e-4f77-b914-211e66f405de</t>
         </is>
@@ -6058,22 +6094,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 [~5]</t>
+          <t>f,N,d,df+2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 [~5]</t>
+          <t>f,N,d,df+2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Black Uppercut [Tag]</t>
+          <t>Black Uppercut</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Black Uppercut [Tag]</t>
+          <t>Black Uppercut</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6148,10 +6184,15 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>a8dc87c6-a861-4aaa-8dad-11837b6c7bc8</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>87622d86-0600-4d62-aa3e-207df964b9f2</t>
         </is>
@@ -6243,12 +6284,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>affb34a7-e60d-4a7e-8163-a3b5eb44de2a</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>158306b3-d011-4b39-baca-39fd54c5b9a9</t>
         </is>
@@ -6305,12 +6346,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>b6cfe340-846a-4801-9a05-3f1cca623e87</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>d284ce92-45c6-47a0-8d47-443d65da0213</t>
         </is>
@@ -6402,12 +6443,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>62e2222a-d767-447c-9597-cd42ee6ba740</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>e16eb5b2-5bce-4471-b4d2-0803b5ff9c52</t>
         </is>
@@ -6504,12 +6545,12 @@
           <t>CSc MS</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>979193c8-6932-47b4-9fa4-b9003eebcf4b</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>f1d64828-18e7-4efd-a0e7-0f7704ce8b6e</t>
         </is>
@@ -6606,12 +6647,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>33dae582-783a-4ade-9e06-f4d4a6bd8db7</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>7122f3d3-7724-4fbf-83b3-41dbcc378184</t>
         </is>
@@ -6713,12 +6754,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>32e9a316-9da6-4279-abda-04a129556b1b</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>20266823-02ce-4d1e-8557-81e8c64c776a</t>
         </is>
@@ -6785,12 +6826,12 @@
           <t>Will throw when hitting a standing opponent. Damage of the throw is 45. Only tags after a throw.</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>5c846483-7a94-4e07-852c-b5845d537912</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>70416c39-20c8-4513-b8dd-e9bd70b28244</t>
         </is>
@@ -6897,12 +6938,12 @@
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>08863484-fc61-4116-a508-06cebfeb070b</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>78589d53-bf16-4b3b-bb20-ef0c133dcf2b</t>
         </is>
@@ -7004,17 +7045,17 @@
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit. Damage of the 3rd Kick will be 5 instead of 7.</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>d8c55bfd-706a-462e-bccd-a00834fb9df7</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>9c52c4ad-26dc-4026-8fea-3e6ead3c968b</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>08863484-fc61-4116-a508-06cebfeb070b</t>
         </is>
@@ -7106,12 +7147,12 @@
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>9bcabe9f-96cf-4b46-88b9-80a0c662fcbe</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>f6dbfada-e197-4da8-ba6c-52a1d59dfff1</t>
         </is>
@@ -7203,17 +7244,17 @@
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit. Damage of the 3rd Kick will be 5 instead of 7.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>806993be-4cbc-4958-bd89-765cfe57f186</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>c116264a-8f45-4af9-b7ea-ce545d7d81c7</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>9bcabe9f-96cf-4b46-88b9-80a0c662fcbe</t>
         </is>
@@ -7305,12 +7346,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>c3cc969f-1b6a-438e-a779-ba3073936029</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>ffd56f21-871c-49b0-9b51-2b84c91407b2</t>
         </is>
@@ -7407,12 +7448,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>b476ed63-a2ab-4600-8a8b-4e5dd32f0c6e</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>ed75a046-6aba-48e0-bdde-b6991c6b4d1f</t>
         </is>
@@ -7504,12 +7545,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>f7674cff-51a4-48e4-a31f-3e03977c6507</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>6f8e7c99-c92f-4b3c-aa02-1b22599e4e17</t>
         </is>
@@ -7606,12 +7647,12 @@
           <t>SH GB</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>51604ea2-c28f-4cb0-95d7-ac8dbfbd7fa7</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>979985ff-1a05-45a1-9137-7cd991b27189</t>
         </is>
@@ -7708,12 +7749,12 @@
           <t>Armor King will be FCD is the move whiffs. On a hit or block he will get up instantly.</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>86fad0be-3d5f-4f68-a602-4e4b6028cab6</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>9c38feef-3fd2-4bc3-aa75-7a6542f91764</t>
         </is>
@@ -7845,20 +7886,25 @@
       </c>
       <c r="X89" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y89" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y89" s="1" t="inlineStr">
+      <c r="Z89" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z89" s="1" t="inlineStr">
+      <c r="AA89" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA89" s="1" t="inlineStr">
+      <c r="AB89" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7950,12 +7996,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>79ef7239-c7b9-4378-9e5a-0ffc387c9e30</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>5f3c656f-fbd7-4c37-b3f3-4387482fe5a0</t>
         </is>
@@ -8007,12 +8053,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>2f203f17-6193-4426-8b18-6cde3317114b</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>258daaad-b92a-4b06-af9b-d7aed1e0c7ce</t>
         </is>
@@ -8104,12 +8150,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>91ca551c-67f1-4ce9-8585-0ed4f2b757a3</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>83c02aa7-b86b-4b97-a898-ebffbfe5d7b1</t>
         </is>
@@ -8241,20 +8287,25 @@
       </c>
       <c r="X95" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y95" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Z95" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="AA95" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AB95" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8306,12 +8357,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8358,17 +8409,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8415,17 +8466,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AB98" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8472,17 +8523,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8529,17 +8580,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8671,20 +8722,25 @@
       </c>
       <c r="X103" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y103" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8726,12 +8782,12 @@
           <t>hhmmhLLLmm</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
         </is>
       </c>
-      <c r="AA104" t="inlineStr">
+      <c r="AB104" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8773,12 +8829,12 @@
           <t>hmmhLLLmm</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
-      <c r="AA105" t="inlineStr">
+      <c r="AB105" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/armorking_step7.xlsx
+++ b/sources/armorking_step7.xlsx
@@ -7988,12 +7988,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">

--- a/sources/armorking_step7.xlsx
+++ b/sources/armorking_step7.xlsx
@@ -1365,6 +1365,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
@@ -1417,6 +1422,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
@@ -1474,6 +1484,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
@@ -1536,6 +1551,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
@@ -1598,6 +1618,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
@@ -1665,6 +1690,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
@@ -1727,6 +1757,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
@@ -1787,6 +1822,11 @@
       <c r="U20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -8357,6 +8397,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
+        </is>
+      </c>
       <c r="Z96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
@@ -8409,6 +8454,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
+        </is>
+      </c>
       <c r="Z97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
@@ -8466,6 +8516,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
+        </is>
+      </c>
       <c r="Z98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
@@ -8523,6 +8578,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
+        </is>
+      </c>
       <c r="Z99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
@@ -8578,6 +8638,11 @@
       <c r="U100" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
@@ -8782,6 +8847,11 @@
           <t>hhmmhLLLmm</t>
         </is>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>21571b37-4525-4b34-9433-0797a86f473f</t>
+        </is>
+      </c>
       <c r="Z104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
@@ -8827,6 +8897,11 @@
       <c r="S105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">

--- a/sources/armorking_step7.xlsx
+++ b/sources/armorking_step7.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB105"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="61" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="61" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="133" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="133" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Coconut Crush</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Coconut Crush</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>f9ce71ca-5aa2-4481-be55-3310546052c7</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0f9bdab1-75b2-4228-a53f-f0a45e37e195</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Suplex</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Suplex</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>5fc6512a-4404-42e6-80c3-2fc278d4455b</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>06dc090e-c5ae-46e1-a19f-d04e3a8a5207</t>
         </is>
@@ -744,57 +750,57 @@
           <t>2+4,d,d,D+1+2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Steiner's Srewdriver</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Steiner's Srewdriver</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>898e20e1-c3e0-43e8-8566-cecbdaf86347</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>8c7def3b-7c4e-4924-8394-4e591d86c38d</t>
         </is>
@@ -811,62 +817,62 @@
           <t>qcf+1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Jaguar Driver</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Jaguar Driver</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>(1_3+4)</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>After the initial grab, escape with 3+4.</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2ab01235-e3c3-4afb-af8d-794284dc99c9</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>aacf4303-5f8c-448b-8b48-aca54f9326dd</t>
         </is>
@@ -883,62 +889,62 @@
           <t>f,hcf+1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Giant Swing</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Giant Swing</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Can be Tech Rolled to reduce damage by half.</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>58992924-7087-47b9-a190-320799679b61</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>6caca9f4-1eb2-4e32-8bc0-fa8bf330f264</t>
         </is>
@@ -955,57 +961,57 @@
           <t>db,DB+1+2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>DDT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>DDT</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>b6c967e2-9ac1-4908-863a-fcb1b0ecf168</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>f5bd83e9-96be-449f-825e-dc066deabe14</t>
         </is>
@@ -1022,57 +1028,57 @@
           <t>db,F+2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Tombstone Piledriver</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Tombstone Piledriver</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>a1c92638-4a1a-412d-b86d-9d6ba82425dc</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>4cd6c89f-9faf-40a3-b3b9-43495afc8252</t>
         </is>
@@ -1096,65 +1102,70 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>DB+2+4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Armor King's Drver</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Armor King's Drver</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Special Tag Throw with King only. King finishes with a Dive Bomb. Total damage is 32.; Also use 2 to escape after the initial grab.</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>f593dcd2-96d4-4be9-9a67-c91c86c3b679</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>222011b9-5903-46a3-8fa1-df6f46daa34a</t>
         </is>
@@ -1171,67 +1182,67 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Duck</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Only throws in close range against a standing opponent. Cannot be escaped or blocked.</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>120ce26e-0aee-46de-bdb2-d6d6b18c626e</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>837014c6-6dee-4ee6-98ca-785113dbadf2</t>
         </is>
@@ -1255,60 +1266,65 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>db+2+4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Mount</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Mount</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Ground</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Can be done on a face down or face up opponent.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>0d4f502a-09d2-47d8-82ae-55e64c6b84dc</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
@@ -1332,50 +1348,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>DB+1+2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Ultimate Tackle</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1392,52 +1413,62 @@
           <t>FC+1+2,1,2,1,2,1</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>FC+1+2,1,2,1,1,2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1454,52 +1485,62 @@
           <t>FC+1+2,2,1,2,2,1</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2,1,2,1,2</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>FC+1+2,2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>– Ultimate Punches</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Ultimate Tackle – Ultimate Punches</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>5,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1516,57 +1557,57 @@
           <t>db+1+3,1,2,1,2,1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>– Mounted Punches</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Mount – Mounted Punches</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>-,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1583,57 +1624,57 @@
           <t>db+1+3,2,1,2,1,2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>– Mounted Punches</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Mount – Mounted Punches</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>5,5,5,5,5</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>-,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>f2362b41-81bb-4572-9612-c6f034acc9c3</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1657,50 +1698,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Reverse Death Valley Bomb</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Reverse Death Valley Bomb</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1724,50 +1770,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Lifting Reverse DDT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lifting Reverse DDT</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1791,50 +1842,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Reverse DDT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Reverse DDT</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1866,125 +1922,130 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="K23" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="M23" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="N23" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="Q23" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q23" s="1" t="inlineStr">
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
+      <c r="S23" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S23" s="1" t="inlineStr">
+      <c r="T23" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T23" s="1" t="inlineStr">
+      <c r="U23" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U23" s="1" t="inlineStr">
+      <c r="V23" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V23" s="1" t="inlineStr">
+      <c r="W23" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
+      <c r="X23" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X23" s="1" t="inlineStr">
+      <c r="Y23" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr">
+      <c r="Z23" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z23" s="1" t="inlineStr">
+      <c r="AA23" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA23" s="1" t="inlineStr">
+      <c r="AB23" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB23" s="1" t="inlineStr">
+      <c r="AC23" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2001,77 +2062,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>425ecead-c5f5-4fae-b77d-422ca2afe090</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>a9e68546-0185-46ef-8ed4-8a0b9b10aa49</t>
         </is>
@@ -2088,77 +2149,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>3fe6d4bf-a051-4506-a70d-2bf2a0526aaa</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>454bb85d-4210-448b-80aa-39b229c5b159</t>
         </is>
@@ -2175,77 +2236,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>7b3c7523-179a-4243-b4ff-d95c3cf7da7f</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>f3bb5aa5-066e-488e-bb8c-b05561279e2e</t>
         </is>
@@ -2262,77 +2323,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>c44668fe-5287-4604-88c1-28460e83c16f</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>098a9278-c701-4eaf-a813-84fababab275</t>
         </is>
@@ -2349,77 +2410,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>b099ff65-2292-4306-9641-5df82371cb4d</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2e7f3c76-a21f-422c-bce4-6f6b03b4d2eb</t>
         </is>
@@ -2436,77 +2497,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>46306ede-df09-4fd4-a22e-683590bcc90f</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>f5f5e160-785c-4d03-9348-c3e64c3ec8d8</t>
         </is>
@@ -2523,77 +2584,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>a5af8aee-cfb9-4150-9900-97663eaa005d</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>84e6cfd8-06a4-4792-b69b-7138dd47e6c5</t>
         </is>
@@ -2610,77 +2671,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>e86479f4-aaff-4cbe-a1d3-048dbb9eaf30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>5070b82d-e58b-4c7b-a0f9-0db46531428d</t>
         </is>
@@ -2697,77 +2758,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>35d7bc20-c87c-4517-bc1c-0718d5232806</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>3265579b-e039-45b2-b901-9e081e404889</t>
         </is>
@@ -2784,77 +2845,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>380565ba-6f89-41ce-a448-c96ec4e77671</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>b030046c-efd4-4e98-bf03-7bd02c053fb1</t>
         </is>
@@ -2871,77 +2932,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>d9b549e9-607b-44a3-b65e-a96ad7a21365</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>c2aa915b-99b3-4dec-8030-b347566d7683</t>
         </is>
@@ -2958,77 +3019,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>eb3d8898-b370-4c3e-b890-36b9d527e7e0</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>ff3d8574-2231-47c3-9a23-da6397dfb5e2</t>
         </is>
@@ -3045,77 +3106,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>c1100dcd-7386-4729-976f-94d0c10e01b7</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>110de783-241f-4434-9ee9-b2f2282b625e</t>
         </is>
@@ -3132,77 +3193,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>68169812-6f33-4587-af9b-01f1197d41fe</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>db4c65d5-8db1-4306-8971-3e405e45dcaa</t>
         </is>
@@ -3219,77 +3280,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>80fb6cea-14ab-4952-b3c4-cc15052db610</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>9ab80fdd-fb6e-4c05-8778-dc2ff8a34308</t>
         </is>
@@ -3306,77 +3367,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>b0c18e86-cf15-46cb-9294-c345ce136d3a</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>79956f02-d230-4a3d-a91e-2278f1bc39ce</t>
         </is>
@@ -3393,77 +3454,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2390f9cd-e831-4fcf-9a97-c7ac631288eb</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>5f415e40-13fc-4adb-bfc4-cbe236d5cb6e</t>
         </is>
@@ -3480,77 +3541,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2bc4d065-9808-467d-b2ef-0dc9c98d6bc3</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>8442cf78-2ba8-4d81-9954-ff712f6c6bbb</t>
         </is>
@@ -3567,77 +3628,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>0048037f-4c9a-4ac7-ab8d-8d77f35ec379</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>07e44464-e8a6-43d0-b162-9ebf83073f23</t>
         </is>
@@ -3654,77 +3715,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>4ed88471-48fb-4424-b1d6-4ff05a9eafaf</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>e3b89a0c-60bc-481a-bbab-fc07eb530c67</t>
         </is>
@@ -3741,77 +3802,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>dc7b170d-9a9b-4eae-aa45-d04a9b9644b6</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>8ef29abb-51a1-4f64-b660-25cbee7be486</t>
         </is>
@@ -3828,77 +3889,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>a3f049e9-03a1-4863-aff8-6c62b22bd98e</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>bba8a28b-8fcf-4ab3-821e-44e475d24c1b</t>
         </is>
@@ -3915,77 +3976,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>9c8a2371-7cb5-4c03-9d9c-3e7be29224ca</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>14230b82-617c-4a26-9e9f-0c73ee47a678</t>
         </is>
@@ -4002,77 +4063,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>60bba712-65b9-4363-aa67-702066fa212f</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>a62d95a8-d7d1-4730-9a9f-869030cdab23</t>
         </is>
@@ -4104,125 +4165,130 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="F50" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="H50" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H50" s="1" t="inlineStr">
+      <c r="I50" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I50" s="1" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J50" s="1" t="inlineStr">
+      <c r="K50" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K50" s="1" t="inlineStr">
+      <c r="L50" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L50" s="1" t="inlineStr">
+      <c r="M50" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M50" s="1" t="inlineStr">
+      <c r="N50" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N50" s="1" t="inlineStr">
+      <c r="O50" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O50" s="1" t="inlineStr">
+      <c r="P50" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P50" s="1" t="inlineStr">
+      <c r="Q50" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q50" s="1" t="inlineStr">
+      <c r="R50" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R50" s="1" t="inlineStr">
+      <c r="S50" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S50" s="1" t="inlineStr">
+      <c r="T50" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T50" s="1" t="inlineStr">
+      <c r="U50" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U50" s="1" t="inlineStr">
+      <c r="V50" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V50" s="1" t="inlineStr">
+      <c r="W50" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W50" s="1" t="inlineStr">
+      <c r="X50" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X50" s="1" t="inlineStr">
+      <c r="Y50" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y50" s="1" t="inlineStr">
+      <c r="Z50" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z50" s="1" t="inlineStr">
+      <c r="AA50" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA50" s="1" t="inlineStr">
+      <c r="AB50" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB50" s="1" t="inlineStr">
+      <c r="AC50" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -4239,92 +4305,92 @@
           <t>b+1</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Parting Chop</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Parting Chop</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>9f288870-b237-4a2d-9722-8b59e043436a</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>354dab8e-e02a-44ab-82d3-b5d712e003f3</t>
         </is>
@@ -4341,92 +4407,92 @@
           <t>f,N,d,df+1</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Shadow Lariat</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Shadow Lariat</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>a27064f0-da8a-4052-9014-478c07cbcb87</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>03cecdef-ae4e-408f-854b-172d760e9a7e</t>
         </is>
@@ -4443,92 +4509,92 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Elbow Knife</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Elbow Knife</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>CS OBc</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>26f5fa66-8a0a-447d-b39a-41b0316ce295</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>bfecad09-d073-4d08-9852-f9229a38f6a9</t>
         </is>
@@ -4552,85 +4618,90 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>d+1,N+2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Low Jab - Upper</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Low Jab - Upper</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>8 x</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>8 x</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>-2 -9</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-2 -9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+9 +2</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>sm</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>sm</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>74775d6a-29fb-4bd6-ad28-d2be38f2e7bb</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>8e181d74-9595-4d22-83f1-5b83615ace7f</t>
         </is>
@@ -4647,87 +4718,87 @@
           <t>1,2</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>+2 0</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>+2 0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>+7 +6</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>+7 +6</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+7 +6</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+7 +6</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>6,10</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>6,10</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>9633cdef-e24e-4676-9299-3d28d609372a</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>617d3195-98c8-4793-95df-e76d67a1d361</t>
         </is>
@@ -4744,87 +4815,87 @@
           <t>1,2,1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Double Punch - Upper</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Double Punch - Upper</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>8 x x</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>8 x x</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>+2 0 0</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>+2 0 0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>+7 +6 +11</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>6,10,10</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>6,10,10</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>bf774eab-e828-4478-b478-d08b88a510b1</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>689069d7-667f-4b36-9163-718de6d1238d</t>
         </is>
@@ -4841,92 +4912,92 @@
           <t>d+1+2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Corporate Elbow</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Corporate Elbow</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>fd968785-ece3-47a5-92fc-a0d72a0c858b</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>11ed2db5-bd38-4efe-a4ca-8880fd7755c7</t>
         </is>
@@ -4943,87 +5014,87 @@
           <t>WS+1+2</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Quick Upper</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Quick Upper</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>6fec99ce-a280-4022-936b-d6a726d2c00e</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>e6281cae-4def-47e4-9be4-e118aa916f62</t>
         </is>
@@ -5040,92 +5111,92 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Elbow Sting</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Elbow Sting</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>GB SLDc</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>00e3804b-a60e-4c84-a177-cd15e4735427</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>092be268-ab49-4fc0-887b-5709b7e8e802</t>
         </is>
@@ -5142,97 +5213,97 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Flying Cross Chop</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Flying Cross Chop</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>(-5_-25)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>(-5_-25)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>(h_l)</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>(h_l)</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Hits high at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>dca3e8a7-3253-4beb-859f-f86a91cec02e</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>39d604fa-caf6-4a30-a9ca-73c996e26573</t>
         </is>
@@ -5256,90 +5327,95 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>F+1+2; WR+F+1+2; uf+1+2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>4336aca8-72e9-4de4-b567-00182e4e297d</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>0704d26e-9310-4446-b785-4426d468365b</t>
         </is>
@@ -5356,52 +5432,52 @@
           <t>uf,N+1+2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Jump In Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Jump In Knuckle Bomb</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>cd1e647b-0556-484d-b641-a13ba2b71ae2</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>74f706f4-4a47-403c-a8df-f18096ac7a1b</t>
         </is>
@@ -5418,92 +5494,92 @@
           <t>b+1+4</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Black Arrow</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Black Arrow</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>ee74f26d-769f-4df4-bbf7-7fbfb610cb9d</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>f057c9e7-f1c1-4078-995e-999034d6faf2</t>
         </is>
@@ -5520,97 +5596,97 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Black Shoulder Tackle</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Black Shoulder Tackle</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Leaves Armor King in Back Turned Position when the opponent blocks.</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>20573691-9a78-457b-8baa-ffefe9b25044</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>ca61d1a0-8d2e-46a4-98d2-0c035f774084</t>
         </is>
@@ -5627,97 +5703,97 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Smash Upper</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Smash Upper</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>d11f5d19-7db2-4b0d-9b48-f6223d76772c</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>399faacb-83da-489a-a3c7-9b838d5a639e</t>
         </is>
@@ -5734,87 +5810,87 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Elbow Gut Punch</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Elbow Gut Punch</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>ebc76774-237e-42af-a946-361b5f39d9d8</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>3dbdcaa6-2488-4c15-8b53-dc33d7481626</t>
         </is>
@@ -5831,92 +5907,92 @@
           <t>f,f,N+2</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Ground Smash</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Ground Smash</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>DSc</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>f8b49771-5fca-4a5b-b0a8-10bed196b340</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>287a4d40-0c80-4ea4-991c-66aaefa1e92e</t>
         </is>
@@ -5933,97 +6009,97 @@
           <t>FC+df+2</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Dynamite Upper</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Dynamite Upper</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>69af551b-4c75-4614-a04f-ce032a2aff16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>765ac45b-a790-43b3-84fb-8b5da4cfe515</t>
         </is>
@@ -6040,92 +6116,92 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Swipe</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Swipe</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>390963d5-ab9b-4abe-b87d-b8b588084767</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>c55fd6d7-722e-4f77-b914-211e66f405de</t>
         </is>
@@ -6142,97 +6218,97 @@
           <t>f,N,d,df+2</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Black Uppercut</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Black Uppercut</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>a8dc87c6-a861-4aaa-8dad-11837b6c7bc8</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>87622d86-0600-4d62-aa3e-207df964b9f2</t>
         </is>
@@ -6249,87 +6325,87 @@
           <t>2,1</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Straight Right - Elbow</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Straight Right - Elbow</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>10 x</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>10 x</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>+6 +6</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>+6 +6</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>+6 +6</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>+6 +6</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>affb34a7-e60d-4a7e-8163-a3b5eb44de2a</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>158306b3-d011-4b39-baca-39fd54c5b9a9</t>
         </is>
@@ -6353,45 +6429,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>u+2+4; uf+2+4</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Elbow Drop</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Elbow Drop</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>b6cfe340-846a-4801-9a05-3f1cca623e87</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>d284ce92-45c6-47a0-8d47-443d65da0213</t>
         </is>
@@ -6408,87 +6489,87 @@
           <t>b+3</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Toll Kick</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Toll Kick</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>62e2222a-d767-447c-9597-cd42ee6ba740</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>e16eb5b2-5bce-4471-b4d2-0803b5ff9c52</t>
         </is>
@@ -6505,92 +6586,92 @@
           <t>BK 3</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Blind Kick</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Blind Kick</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>CSc MS</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>979193c8-6932-47b4-9fa4-b9003eebcf4b</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>f1d64828-18e7-4efd-a0e7-0f7704ce8b6e</t>
         </is>
@@ -6607,92 +6688,92 @@
           <t>f,f+3+4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>33dae582-783a-4ade-9e06-f4d4a6bd8db7</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>7122f3d3-7724-4fbf-83b3-41dbcc378184</t>
         </is>
@@ -6716,90 +6797,95 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>f,f,f+3+4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Satellite Exploder</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Satellite Exploder</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>32e9a316-9da6-4279-abda-04a129556b1b</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>20266823-02ce-4d1e-8557-81e8c64c776a</t>
         </is>
@@ -6816,62 +6902,62 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Frankensteiner</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>Will throw when hitting a standing opponent. Damage of the throw is 45. Only tags after a throw.</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>5c846483-7a94-4e07-852c-b5845d537912</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>70416c39-20c8-4513-b8dd-e9bd70b28244</t>
         </is>
@@ -6895,95 +6981,100 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>D,df+4,4,4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Ali Kicks</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Ali Kicks</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>16 x</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>16 x</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>13_17,7,7</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>13_17,7,7</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>08863484-fc61-4116-a508-06cebfeb070b</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>78589d53-bf16-4b3b-bb20-ef0c133dcf2b</t>
         </is>
@@ -7000,102 +7091,102 @@
           <t>d+3+4,4,4,4,4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>– Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Ali Kicks – Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>x x</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>16 x</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>x -35</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-29 -35 -35 x -35</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-13 -19 +6 x KD</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>-13 -19 +6 x KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>13_17,7,7,4,3</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>LLLLL</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>CH RC</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit. Damage of the 3rd Kick will be 5 instead of 7.</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>d8c55bfd-706a-462e-bccd-a00834fb9df7</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>9c52c4ad-26dc-4026-8fea-3e6ead3c968b</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>08863484-fc61-4116-a508-06cebfeb070b</t>
         </is>
@@ -7112,87 +7203,87 @@
           <t>uf,N+3+4,4,4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Jump In Ali Kicks</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Jump In Ali Kicks</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-29 -35 -35</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>-13 -19 +6</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>17,7,7</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>17,7,7</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>9bcabe9f-96cf-4b46-88b9-80a0c662fcbe</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>f6dbfada-e197-4da8-ba6c-52a1d59dfff1</t>
         </is>
@@ -7209,92 +7300,92 @@
           <t>uf,N+3+4,4,4,4,4</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>– Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Jump In Ali Kicks – Extended Ali Kicks</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>x -35</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-29 -35 -35 x -35</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-13 -19 +6 x KD</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>-13 -19 +6 x KD</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>17,7,7,4,3</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>LLLLL</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>CH RC</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit. Damage of the 3rd Kick will be 5 instead of 7.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>806993be-4cbc-4958-bd89-765cfe57f186</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>c116264a-8f45-4af9-b7ea-ce545d7d81c7</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>9bcabe9f-96cf-4b46-88b9-80a0c662fcbe</t>
         </is>
@@ -7311,87 +7402,87 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Double Knee Drop</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Double Knee Drop</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>c3cc969f-1b6a-438e-a779-ba3073936029</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>ffd56f21-871c-49b0-9b51-2b84c91407b2</t>
         </is>
@@ -7408,92 +7499,92 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Neck Cutter Kick</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Neck Cutter Kick</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>b476ed63-a2ab-4600-8a8b-4e5dd32f0c6e</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>ed75a046-6aba-48e0-bdde-b6991c6b4d1f</t>
         </is>
@@ -7510,87 +7601,87 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Konvict Kick</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Konvict Kick</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>f7674cff-51a4-48e4-a31f-3e03977c6507</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>6f8e7c99-c92f-4b3c-aa02-1b22599e4e17</t>
         </is>
@@ -7607,92 +7698,92 @@
           <t>f,N,d,df+4</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Black Knee Rising</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Black Knee Rising</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>SH GB</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>51604ea2-c28f-4cb0-95d7-ac8dbfbd7fa7</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>979985ff-1a05-45a1-9137-7cd991b27189</t>
         </is>
@@ -7709,92 +7800,92 @@
           <t>db+4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Roaring Drop Kick</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Roaring Drop Kick</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Armor King will be FCD is the move whiffs. On a hit or block he will get up instantly.</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>86fad0be-3d5f-4f68-a602-4e4b6028cab6</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>9c38feef-3fd2-4bc3-aa75-7a6542f91764</t>
         </is>
@@ -7826,125 +7917,130 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E89" s="1" t="inlineStr">
+      <c r="F89" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
+      <c r="G89" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
+      <c r="H89" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H89" s="1" t="inlineStr">
+      <c r="I89" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I89" s="1" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J89" s="1" t="inlineStr">
+      <c r="K89" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K89" s="1" t="inlineStr">
+      <c r="L89" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L89" s="1" t="inlineStr">
+      <c r="M89" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M89" s="1" t="inlineStr">
+      <c r="N89" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N89" s="1" t="inlineStr">
+      <c r="O89" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O89" s="1" t="inlineStr">
+      <c r="P89" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P89" s="1" t="inlineStr">
+      <c r="Q89" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q89" s="1" t="inlineStr">
+      <c r="R89" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R89" s="1" t="inlineStr">
+      <c r="S89" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S89" s="1" t="inlineStr">
+      <c r="T89" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T89" s="1" t="inlineStr">
+      <c r="U89" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U89" s="1" t="inlineStr">
+      <c r="V89" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V89" s="1" t="inlineStr">
+      <c r="W89" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W89" s="1" t="inlineStr">
+      <c r="X89" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X89" s="1" t="inlineStr">
+      <c r="Y89" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y89" s="1" t="inlineStr">
+      <c r="Z89" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z89" s="1" t="inlineStr">
+      <c r="AA89" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA89" s="1" t="inlineStr">
+      <c r="AB89" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB89" s="1" t="inlineStr">
+      <c r="AC89" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7961,87 +8057,87 @@
           <t>uf+1+2~D</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>79ef7239-c7b9-4378-9e5a-0ffc387c9e30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>5f3c656f-fbd7-4c37-b3f3-4387482fe5a0</t>
         </is>
@@ -8058,47 +8154,47 @@
           <t>uf,N+1+2~D</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>2f203f17-6193-4426-8b18-6cde3317114b</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>258daaad-b92a-4b06-af9b-d7aed1e0c7ce</t>
         </is>
@@ -8115,87 +8211,87 @@
           <t>uf,N+1+4</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Jump In Moon Shot Drop</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Jump In Moon Shot Drop</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>91ca551c-67f1-4ce9-8585-0ed4f2b757a3</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>83c02aa7-b86b-4b97-a898-ebffbfe5d7b1</t>
         </is>
@@ -8227,125 +8323,130 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="F95" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="H95" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="I95" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I95" s="1" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="K95" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K95" s="1" t="inlineStr">
+      <c r="L95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L95" s="1" t="inlineStr">
+      <c r="M95" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="N95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="O95" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="P95" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="Q95" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="S95" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="T95" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="U95" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="V95" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
+      <c r="W95" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W95" s="1" t="inlineStr">
+      <c r="X95" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="Y95" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Z95" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="AA95" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AB95" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
+      <c r="AC95" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8362,52 +8463,52 @@
           <t>f,N,d,df+1+2</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Choke Sleeper</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Choke Sleeper</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="V96" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8424,52 +8525,52 @@
           <t>f,N,d,df+1+2,2+4,1+2,1+2</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>– Funeral Suplex</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Choke Sleeper – Funeral Suplex</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>32,25</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8486,52 +8587,52 @@
           <t>f,N,d,df+1+2,3+4,3+4,1+2</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>– Pickpocket Sleeper</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Choke Sleeper – Pickpocket Sleeper</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>32,15</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AB98" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AC98" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8548,52 +8649,52 @@
           <t>f,N,d,df+1+2,3+4,3+4,1+2,1,1,1+2</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>–– Triple Mounted Punches</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Choke Sleeper – Pickpocket Sleeper – Triple Mounted Punches</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>4,4,12</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>32,15,4,4,12</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="V99" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
+      <c r="AC99" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8610,52 +8711,52 @@
           <t>f,N,d,df+1+2,3+4,3+4,1+2,3,4,1+2,3+4</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>–– Stretch Muffler</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Choke Sleeper – Pickpocket Sleeper – Stretch Muffler</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>32,15,23</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AC100" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8687,125 +8788,130 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H103" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I103" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K103" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L103" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N103" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q103" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T103" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U103" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V103" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W103" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X103" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB103" s="1" t="inlineStr">
+      <c r="AC103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8822,42 +8928,42 @@
           <t>1,2,1,1,2,4,4,4,1,3</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>6,10,10,6,6,5,5,5,7,24</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>6,10,10,6,6,5,5,5,7,24</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>hhmmhLLLmm</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>hhmmhLLLmm</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
+      <c r="AC104" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -8874,42 +8980,42 @@
           <t>f+2,1,1,2,4,4,4,1,3</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>15,10,6,6,5,5,5,7,24</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>15,10,6,6,5,5,5,7,24</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AC105" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
